--- a/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N44_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G2/G2_T3380_W0028F0002T0006Z000C1N44_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.63204156995489</v>
+        <v>5.465206755117669</v>
       </c>
       <c r="D2" t="n">
-        <v>33.28367256570466</v>
+        <v>5.408596791927008</v>
       </c>
       <c r="E2" t="n">
-        <v>8.68408918704294</v>
+        <v>1.411164492894478</v>
       </c>
       <c r="F2" t="n">
-        <v>8.999816148352082</v>
+        <v>1.462470124107213</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>23.10161074659613</v>
+        <v>3.754011746321871</v>
       </c>
       <c r="D3" t="n">
-        <v>22.81596107226496</v>
+        <v>3.707593674243056</v>
       </c>
       <c r="E3" t="n">
-        <v>8.68408918704294</v>
+        <v>1.411164492894478</v>
       </c>
       <c r="F3" t="n">
-        <v>8.999816148352082</v>
+        <v>1.462470124107213</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>11.73015067551327</v>
+        <v>1.906149484770906</v>
       </c>
       <c r="D4" t="n">
-        <v>11.48938995444546</v>
+        <v>1.867025867597387</v>
       </c>
       <c r="E4" t="n">
-        <v>8.68408918704294</v>
+        <v>1.411164492894478</v>
       </c>
       <c r="F4" t="n">
-        <v>8.999816148352082</v>
+        <v>1.462470124107213</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.75195535696963</v>
+        <v>2.234692745507565</v>
       </c>
       <c r="D5" t="n">
-        <v>11.79850835800993</v>
+        <v>1.917257608176614</v>
       </c>
       <c r="E5" t="n">
-        <v>8.68408918704294</v>
+        <v>1.411164492894478</v>
       </c>
       <c r="F5" t="n">
-        <v>8.999816148352082</v>
+        <v>1.462470124107213</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
